--- a/Test Specification.xlsx
+++ b/Test Specification.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20385" windowHeight="7950" activeTab="3"/>
+    <workbookView windowWidth="20385" windowHeight="7950" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Min A - Max A" sheetId="2" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="Min A" sheetId="6" r:id="rId4"/>
     <sheet name="Min B" sheetId="7" r:id="rId5"/>
     <sheet name="Max A" sheetId="8" r:id="rId6"/>
+    <sheet name="LOQ" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70">
   <si>
     <t>Scenario 1:
 Whole Number</t>
@@ -741,6 +742,195 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> (Decimal  Number)</t>
+    </r>
+  </si>
+  <si>
+    <t>Limit of  Quantification (LOQ)</t>
+  </si>
+  <si>
+    <t>Entered Result</t>
+  </si>
+  <si>
+    <t>Expected Final Result</t>
+  </si>
+  <si>
+    <t>Min LOQ</t>
+  </si>
+  <si>
+    <t>Max LOQ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Smaller than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Min LOQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(Whole Number)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Smaller than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Min LOQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (Decimal  Number)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Equal to the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Min LOQ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ranges between (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Min LOQ - Max LOQ)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (Whole Number)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ranges between (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Min LOQ - Max LOQ)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> (Decimal Number)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Equal to the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Max LOQ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Greater than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Max LOQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(Whole Number)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Greater than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Max LOQ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(Decimal  Number)</t>
     </r>
   </si>
 </sst>
@@ -749,10 +939,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -816,7 +1006,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -831,7 +1044,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -852,53 +1065,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -907,14 +1083,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -930,9 +1098,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -949,6 +1131,14 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -974,7 +1164,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,180 +1344,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1186,10 +1376,23 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1220,6 +1423,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1244,11 +1460,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1268,32 +1490,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1317,157 +1518,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1477,6 +1693,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1489,13 +1711,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1510,13 +1744,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1855,509 +2089,509 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
-      <c r="A2" s="13"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="19"/>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="8">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="F2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:8">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14">
-        <v>10</v>
-      </c>
-      <c r="C3" s="14">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20">
+        <v>10</v>
+      </c>
+      <c r="C3" s="20">
         <v>20</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>0.154</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:8">
-      <c r="A4" s="13"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="5" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>5</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="13"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="5" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="8">
         <v>5.45</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="F5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="13"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="5" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="8">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="13"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="5" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="8">
         <v>9.9</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="F7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="13"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="5" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="E8" s="8">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="13"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="5" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="8">
         <v>15</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="13"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="5" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="8">
         <v>15.1456</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="F10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="13"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="5" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="8">
         <v>20</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="13"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="5" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="8">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="F12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:8">
-      <c r="A13" s="13"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="5" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="8">
         <v>20.1</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="F13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:8">
-      <c r="A14" s="13"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="5" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="8">
         <v>25</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="F14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:8">
-      <c r="A15" s="13"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="5" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="8">
         <v>22.5456</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="F15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:8">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="1:8">
-      <c r="A18" s="13"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="8">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="F18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" customHeight="1" spans="1:8">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20">
         <v>4.512</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="20">
         <v>5.512</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="8">
         <v>0.154</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="F19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:8">
-      <c r="A20" s="13"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="5" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="8">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="F20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:8">
-      <c r="A21" s="13"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="5" t="s">
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="8">
         <v>3.541</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="F21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:8">
-      <c r="A22" s="13"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="5" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="8">
         <v>4</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="F22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" customHeight="1" spans="1:8">
-      <c r="A23" s="13"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="5" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="8">
         <v>5.511</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="F23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:8">
-      <c r="A24" s="13"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="5" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="8">
         <v>4.512</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="F24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" customHeight="1" spans="1:8">
-      <c r="A25" s="13"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="5" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="8">
         <v>5</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="F25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" customHeight="1" spans="1:8">
-      <c r="A26" s="13"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="5" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="8">
         <v>5.111</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="F26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:8">
-      <c r="A27" s="13"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="5" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="8">
         <v>5.512</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="F27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:8">
-      <c r="A28" s="13"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="5" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="8">
         <v>6</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="F28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:8">
-      <c r="A29" s="13"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="5" t="s">
+      <c r="A29" s="19"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="8">
         <v>5.113</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="F29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:8">
-      <c r="A30" s="13"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="5" t="s">
+      <c r="A30" s="19"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="8">
         <v>7</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="F30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:8">
-      <c r="A31" s="13"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="5" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="8">
         <v>7.546</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="F31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2395,509 +2629,509 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
-      <c r="A2" s="13"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="19"/>
+      <c r="B2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="8">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="F2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:8">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14">
-        <v>10</v>
-      </c>
-      <c r="C3" s="14">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20">
+        <v>10</v>
+      </c>
+      <c r="C3" s="20">
         <v>20</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="8">
         <v>0.154</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="F3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:8">
-      <c r="A4" s="13"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="5" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="8">
         <v>5</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="13"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="5" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="8">
         <v>5.45</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="F5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="13"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="5" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="8">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="13"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="5" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="8">
         <v>9.9</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="F7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="13"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="5" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="E8" s="8">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="13"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="5" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="8">
         <v>15</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="13"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="5" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="8">
         <v>15.1456</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="F10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="13"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="5" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="8">
         <v>20</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="13"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="5" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="8">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="F12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:8">
-      <c r="A13" s="13"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="5" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="8">
         <v>20.1</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="F13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:8">
-      <c r="A14" s="13"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="5" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="8">
         <v>25</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="F14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:8">
-      <c r="A15" s="13"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="5" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="8">
         <v>22.5456</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="F15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:8">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="1:8">
-      <c r="A18" s="13"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="8">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="F18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" customHeight="1" spans="1:8">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20">
         <v>4.512</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="20">
         <v>5.512</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="8">
         <v>0.154</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="F19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:8">
-      <c r="A20" s="13"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="5" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="8">
         <v>3</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="F20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:8">
-      <c r="A21" s="13"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="5" t="s">
+      <c r="A21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="8">
         <v>3.541</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="F21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:8">
-      <c r="A22" s="13"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="5" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="8">
         <v>4</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="F22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" customHeight="1" spans="1:8">
-      <c r="A23" s="13"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="5" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="8">
         <v>5.511</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="F23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:8">
-      <c r="A24" s="13"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="5" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="8">
         <v>4.512</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="F24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" customHeight="1" spans="1:8">
-      <c r="A25" s="13"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="5" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="8">
         <v>5</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="F25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" customHeight="1" spans="1:8">
-      <c r="A26" s="13"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="5" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="8">
         <v>5.111</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="F26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:8">
-      <c r="A27" s="13"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="5" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="8">
         <v>5.512</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="F27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:8">
-      <c r="A28" s="13"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="5" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="8">
         <v>6</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="F28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:8">
-      <c r="A29" s="13"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="5" t="s">
+      <c r="A29" s="19"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="8">
         <v>5.113</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="F29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:8">
-      <c r="A30" s="13"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="5" t="s">
+      <c r="A30" s="19"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="8">
         <v>7</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="F30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:8">
-      <c r="A31" s="13"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="5" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="8">
         <v>7.546</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="F31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2935,672 +3169,672 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="8">
         <v>0</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="H2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
-      <c r="B3" s="7">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="B3" s="10">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10">
         <v>20</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="10">
         <v>30</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="10">
         <v>40</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>0.1547</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="H3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="10" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="H4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="10" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="8">
         <v>5.5452</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="H5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="10" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="6">
-        <v>10</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="8">
+        <v>10</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="10" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="8">
         <v>15</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="10" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="8">
         <v>15.154</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="2"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="10" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="8">
         <v>20</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="H9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="2"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="10" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="8">
         <v>25</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="H10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="2"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="10" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="8">
         <v>25.1454</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="H11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="2"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="8">
         <v>30</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="H12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="2"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="8">
         <v>35</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="2"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="8">
         <v>35.1785</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="2"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="8">
         <v>40</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:10">
       <c r="A16" s="2"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="10" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="8">
         <v>45</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="H16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:10">
       <c r="A17" s="2"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="10" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="8">
         <v>45.1782</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="H17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="8:8">
-      <c r="H18" s="9"/>
+      <c r="H18" s="14"/>
     </row>
     <row r="19" customHeight="1" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:10">
       <c r="A20" s="2"/>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="8">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="H20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:10">
       <c r="A21" s="2"/>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>10.5144</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="10">
         <v>20.1457</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="10">
         <v>30.5456</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="10">
         <v>40.1547</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="8">
         <v>0.154</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="H21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:10">
       <c r="A22" s="2"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="8">
         <v>3</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="H22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
     <row r="23" customHeight="1" spans="1:10">
       <c r="A23" s="2"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="8">
         <v>3.541</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="H23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:10">
       <c r="A24" s="2"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="8">
         <v>10.5144</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="H24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" customHeight="1" spans="1:10">
       <c r="A25" s="2"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="10" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="8">
         <v>15</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="H25" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" customHeight="1" spans="1:10">
       <c r="A26" s="2"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="10" t="s">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="8">
         <v>15.2457</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="H26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:10">
       <c r="A27" s="2"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10" t="s">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="8">
         <v>20.1457</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="H27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:10">
       <c r="A28" s="2"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="10" t="s">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="8">
         <v>25</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="H28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:10">
       <c r="A29" s="2"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="10" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="8">
         <v>25.1245</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="H29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:10">
       <c r="A30" s="2"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="10" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="8">
         <v>30.5456</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="H30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:10">
       <c r="A31" s="2"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="10" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="8">
         <v>35</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="H31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" customHeight="1" spans="1:10">
       <c r="A32" s="2"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="10" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="8">
         <v>35.245</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="H32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
     </row>
     <row r="33" customHeight="1" spans="1:10">
       <c r="A33" s="2"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="10" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="8">
         <v>40.1547</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="1:10">
       <c r="A34" s="2"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="8">
         <v>45</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="H34" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
     </row>
     <row r="35" customHeight="1" spans="1:10">
       <c r="A35" s="2"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="8">
         <v>45.2154</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="H35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3641,268 +3875,268 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="E2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:7">
       <c r="A3" s="2"/>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>0.1547</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="8">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>15.1254</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <v>25</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="E7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>25.1245</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="E8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="5:5">
-      <c r="E9" s="9"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="8">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="2"/>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>20.1457</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="8">
         <v>0.1545</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="E12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="2"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="8">
         <v>19</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="E13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="2"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="8">
         <v>19.5487</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="E14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:7">
       <c r="A15" s="2"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="8">
         <v>20.1457</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="E15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="2"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="8">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="E16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:7">
       <c r="A17" s="2"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="8">
         <v>22.1454</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="E17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3935,268 +4169,268 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="E2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:7">
       <c r="A3" s="2"/>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>0.1547</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="E3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="8">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>15.1254</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <v>25</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="E7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>25.1245</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="E8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="5:5">
-      <c r="E9" s="9"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="8">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="2"/>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>20.1457</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="8">
         <v>0.1545</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="E12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="2"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="8">
         <v>19</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="E13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="2"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="8">
         <v>19.5487</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="E14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:7">
       <c r="A15" s="2"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="8">
         <v>20.1457</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="E15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="2"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="8">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="E16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:7">
       <c r="A17" s="2"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="8">
         <v>22.1454</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="E17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4229,268 +4463,268 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:7">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="E2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:7">
       <c r="A3" s="2"/>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>0.1547</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="8">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="E4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="8">
         <v>15.1254</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="8">
         <v>25</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="8">
         <v>25.1245</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="E8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="5:5">
-      <c r="E9" s="9"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="8">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="E11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="2"/>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>20.1457</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="8">
         <v>0.1545</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="E12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="2"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="8">
         <v>19</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="E13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="2"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="8">
         <v>19.5487</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="E14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:7">
       <c r="A15" s="2"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="8">
         <v>20.1457</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="E15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="2"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="8">
         <v>22</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="E16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:7">
       <c r="A17" s="2"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="8">
         <v>22.1454</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="E17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4502,4 +4736,418 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="26.8857142857143" customWidth="1"/>
+    <col min="2" max="2" width="18.2761904761905" customWidth="1"/>
+    <col min="3" max="3" width="17.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="94.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="19.8571428571429" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.2571428571429" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.4285714285714" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.4952380952381" customWidth="1"/>
+    <col min="9" max="9" width="20.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:9">
+      <c r="A2" s="2"/>
+      <c r="B2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:9">
+      <c r="A3" s="2"/>
+      <c r="B3" s="9">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10">
+        <v>120</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.1547</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:9">
+      <c r="A4" s="2"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="8">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:9">
+      <c r="A5" s="2"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="8">
+        <v>4.2154</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="2"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="8">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>5</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="2"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="8">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="2"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="8">
+        <v>10.2154</v>
+      </c>
+      <c r="F8" s="8">
+        <v>10.2154</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:9">
+      <c r="A9" s="2"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="8">
+        <v>120</v>
+      </c>
+      <c r="F9" s="8">
+        <v>120</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="2"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="8">
+        <v>121</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:9">
+      <c r="A11" s="2"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="8">
+        <v>121.1245</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:7">
+      <c r="B12" s="13"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:9">
+      <c r="A14" s="2"/>
+      <c r="B14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="2"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10">
+        <v>20.1457</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.1545</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:9">
+      <c r="A16" s="2"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="8">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="A17" s="2"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="8">
+        <v>19.5487</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="2"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="8">
+        <v>20.1457</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="2"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="8">
+        <v>22</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="2"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="8">
+        <v>22.1454</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:A11"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C15:C20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <headerFooter/>
+</worksheet>
 </file>